--- a/analysis_sample5.xlsx
+++ b/analysis_sample5.xlsx
@@ -4906,7 +4906,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -4918,8 +4918,11 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4929,6 +4932,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
       </patternFill>
     </fill>
     <fill>
@@ -4954,11 +4962,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5398,7 +5408,7 @@
       <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>0.59</v>
       </c>
       <c r="L2" t="s">
@@ -5416,7 +5426,7 @@
       <c r="P2">
         <v>1.3</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="2">
         <v>322</v>
       </c>
       <c r="R2">
@@ -5454,7 +5464,7 @@
       <c r="J3" t="s">
         <v>36</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>0.51</v>
       </c>
       <c r="L3" t="s">
@@ -5483,7 +5493,7 @@
       <c r="A4" t="s">
         <v>39</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" t="s">
@@ -5498,7 +5508,7 @@
       <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H4" t="s">
@@ -5566,7 +5576,7 @@
       <c r="J5" t="s">
         <v>55</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>0.5</v>
       </c>
       <c r="L5" t="s">
@@ -5584,7 +5594,7 @@
       <c r="P5">
         <v>1.8</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="2">
         <v>347</v>
       </c>
       <c r="R5">
@@ -5651,7 +5661,7 @@
       <c r="A7" t="s">
         <v>66</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" t="s">
@@ -5722,7 +5732,7 @@
       <c r="F8" t="s">
         <v>79</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H8" t="s">
@@ -5731,13 +5741,13 @@
       <c r="I8" t="s">
         <v>82</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="2" t="s">
         <v>83</v>
       </c>
       <c r="K8">
         <v>0.16</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="2" t="s">
         <v>84</v>
       </c>
       <c r="M8" t="s">
@@ -5834,7 +5844,7 @@
       <c r="F10" t="s">
         <v>21</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H10" t="s">
@@ -5843,7 +5853,7 @@
       <c r="I10" t="s">
         <v>102</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="2" t="s">
         <v>103</v>
       </c>
       <c r="K10">
@@ -5920,7 +5930,7 @@
       <c r="P11">
         <v>2.6</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="2">
         <v>312</v>
       </c>
       <c r="R11">
@@ -5958,7 +5968,7 @@
       <c r="J12" t="s">
         <v>120</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>0.66</v>
       </c>
       <c r="L12" t="s">
@@ -5976,7 +5986,7 @@
       <c r="P12">
         <v>2</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="2">
         <v>2082</v>
       </c>
       <c r="R12">
@@ -6017,7 +6027,7 @@
       <c r="K13">
         <v>0.21</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M13" t="s">
@@ -6032,7 +6042,7 @@
       <c r="P13">
         <v>2.6</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="2">
         <v>419</v>
       </c>
       <c r="R13">
@@ -6043,7 +6053,7 @@
       <c r="A14" t="s">
         <v>133</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>5</v>
       </c>
       <c r="C14" t="s">
@@ -6058,7 +6068,7 @@
       <c r="F14" t="s">
         <v>21</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="2" t="s">
         <v>136</v>
       </c>
       <c r="H14" t="s">
@@ -6067,13 +6077,13 @@
       <c r="I14" t="s">
         <v>138</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="2" t="s">
         <v>139</v>
       </c>
       <c r="K14">
         <v>0.5</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="2" t="s">
         <v>140</v>
       </c>
       <c r="M14" t="s">
@@ -6091,7 +6101,7 @@
       <c r="Q14">
         <v>75</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="3">
         <v>0.62</v>
       </c>
     </row>
@@ -6144,7 +6154,7 @@
       <c r="P15">
         <v>1.6</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="2">
         <v>303</v>
       </c>
       <c r="R15">
@@ -6291,7 +6301,7 @@
       <c r="I18" t="s">
         <v>172</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="2" t="s">
         <v>173</v>
       </c>
       <c r="K18">
@@ -6394,7 +6404,7 @@
       <c r="F20" t="s">
         <v>21</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H20" t="s">
@@ -6403,13 +6413,13 @@
       <c r="I20" t="s">
         <v>192</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="2" t="s">
         <v>193</v>
       </c>
       <c r="K20">
         <v>0.17</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="2" t="s">
         <v>194</v>
       </c>
       <c r="M20" t="s">
@@ -6435,7 +6445,7 @@
       <c r="A21" t="s">
         <v>196</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>6</v>
       </c>
       <c r="C21" t="s">
@@ -6577,7 +6587,7 @@
       <c r="K23">
         <v>0.38</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L23" s="2" t="s">
         <v>216</v>
       </c>
       <c r="M23" t="s">
@@ -6648,7 +6658,7 @@
       <c r="P24">
         <v>2.5</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="2">
         <v>450</v>
       </c>
       <c r="R24">
@@ -6659,7 +6669,7 @@
       <c r="A25" t="s">
         <v>226</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>5</v>
       </c>
       <c r="C25" t="s">
@@ -6683,7 +6693,7 @@
       <c r="I25" t="s">
         <v>229</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="2" t="s">
         <v>230</v>
       </c>
       <c r="K25">
@@ -6730,7 +6740,7 @@
       <c r="F26" t="s">
         <v>21</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="2" t="s">
         <v>235</v>
       </c>
       <c r="H26" t="s">
@@ -6739,10 +6749,10 @@
       <c r="I26" t="s">
         <v>237</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="2">
         <v>0.46</v>
       </c>
       <c r="L26" t="s">
@@ -6786,7 +6796,7 @@
       <c r="F27" t="s">
         <v>21</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="2" t="s">
         <v>243</v>
       </c>
       <c r="H27" t="s">
@@ -6795,13 +6805,13 @@
       <c r="I27" t="s">
         <v>245</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="2" t="s">
         <v>246</v>
       </c>
       <c r="K27">
         <v>0.41</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L27" s="2" t="s">
         <v>247</v>
       </c>
       <c r="M27" t="s">
@@ -6851,7 +6861,7 @@
       <c r="I28" t="s">
         <v>252</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="2" t="s">
         <v>253</v>
       </c>
       <c r="K28">
@@ -6898,7 +6908,7 @@
       <c r="F29" t="s">
         <v>21</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="2" t="s">
         <v>258</v>
       </c>
       <c r="H29" t="s">
@@ -6907,7 +6917,7 @@
       <c r="I29" t="s">
         <v>260</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="2" t="s">
         <v>261</v>
       </c>
       <c r="K29">
@@ -6939,7 +6949,7 @@
       <c r="A30" t="s">
         <v>264</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <v>2</v>
       </c>
       <c r="C30" t="s">
@@ -6969,7 +6979,7 @@
       <c r="K30">
         <v>0.96</v>
       </c>
-      <c r="L30" t="s">
+      <c r="L30" s="2" t="s">
         <v>270</v>
       </c>
       <c r="M30" t="s">
@@ -6984,7 +6994,7 @@
       <c r="P30">
         <v>1</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="2">
         <v>348</v>
       </c>
       <c r="R30">
@@ -6995,7 +7005,7 @@
       <c r="A31" t="s">
         <v>272</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
         <v>6</v>
       </c>
       <c r="C31" t="s">
@@ -7022,7 +7032,7 @@
       <c r="J31" t="s">
         <v>276</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="2">
         <v>0.81</v>
       </c>
       <c r="L31" t="s">
@@ -7040,10 +7050,10 @@
       <c r="P31">
         <v>1.8</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="2">
         <v>448</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="3">
         <v>0.5</v>
       </c>
     </row>
@@ -7081,7 +7091,7 @@
       <c r="K32">
         <v>0.4</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L32" s="2" t="s">
         <v>284</v>
       </c>
       <c r="M32" t="s">
@@ -7096,7 +7106,7 @@
       <c r="P32">
         <v>5</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="2">
         <v>1064</v>
       </c>
       <c r="R32">
@@ -7305,7 +7315,7 @@
       <c r="K36">
         <v>0.11</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L36" s="2" t="s">
         <v>315</v>
       </c>
       <c r="M36" t="s">
@@ -7331,7 +7341,7 @@
       <c r="A37" t="s">
         <v>317</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="2">
         <v>6</v>
       </c>
       <c r="C37" t="s">
@@ -7470,7 +7480,7 @@
       <c r="J39" t="s">
         <v>339</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="2">
         <v>0.46</v>
       </c>
       <c r="L39" t="s">
@@ -7488,7 +7498,7 @@
       <c r="P39">
         <v>2.4</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="2">
         <v>532</v>
       </c>
       <c r="R39">
@@ -7611,7 +7621,7 @@
       <c r="A42" t="s">
         <v>360</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="2">
         <v>6</v>
       </c>
       <c r="C42" t="s">
@@ -7638,7 +7648,7 @@
       <c r="J42" t="s">
         <v>364</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="2">
         <v>0.53</v>
       </c>
       <c r="L42" t="s">
@@ -7683,26 +7693,26 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>371</v>
       </c>
     </row>
@@ -13134,65 +13144,65 @@
     <col min="17" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>371</v>
       </c>
     </row>

--- a/analysis_sample5.xlsx
+++ b/analysis_sample5.xlsx
@@ -63,7 +63,7 @@
     <t>Avg Commits</t>
   </si>
   <si>
-    <t>Avg Changes/h</t>
+    <t>Avg Changes/h over session</t>
   </si>
   <si>
     <t>Index</t>
